--- a/output/2026-10-07_18_Serbia_Mačvanski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-07_18_Serbia_Mačvanski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Woby Haus</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski (Vojvode Mišića 79, 15000 Šabac)</t>
@@ -490,10 +489,9 @@
           <t>015/334-120</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore di macchine e utensili, mix professionale/consumer; nessun sito ufficiale reperibile, presenza solo su directory planplus.rs</t>
+          <t>Rivenditore di macchine e utensili, mix professionale/consumer; nessun sito ufficiale reperibile, presenza solo su directory planplus.rs [DUPLICATO — vedi anche: 2026-10-07_01_Serbia_Grad_Beograd_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +506,6 @@
           <t>FiS MB</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski (Masarikova 120, 15000 Šabac)</t>
@@ -524,7 +521,6 @@
           <t>015/354-310</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Attività all'ingrosso oltre che al dettaglio, compatibile con profilo distributore B2B, ma prevalenza utensili da giardinaggio</t>
@@ -542,7 +538,6 @@
           <t>Stil RT</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski (Mačvanska 90, 15000 Šabac; seconda sede Uzveće, Milana Lukića 64, tel 015/449-230)</t>
@@ -558,7 +553,6 @@
           <t>015/341-400</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Dealer multimarca di attrezzature a motore ed elettroutensili professionali (STIHL, Villager, AGM, Black&amp;Decker, DeWalt, Gardena)</t>
@@ -576,7 +570,6 @@
           <t>Dolmar Trade</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Loznica, Mačvanski (Kneza Miloša 29, 15300 Loznica)</t>
@@ -592,7 +585,6 @@
           <t>015/888-140</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dealer STIHL con gamma elettroutensili/macchine, stesso profilo di Stil RT</t>

--- a/output/2026-10-07_18_Serbia_Mačvanski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-07_18_Serbia_Mačvanski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
